--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260626.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260626.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,323,000</t>
+          <t>180,515</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>180,515</t>
+          <t>1,323,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,183,441</t>
+          <t>799,897</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>799,897</t>
+          <t>1,183,441</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>796,000</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>4,906,956</t>
+          <t>796,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>4,906,956</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>316,000</t>
+          <t>992,121</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>992,121</t>
+          <t>316,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>1,739,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>1,739,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>332,000</t>
+          <t>672,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>672,000</t>
+          <t>332,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2239,6 +2239,24 @@
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>-375,426,802</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
